--- a/klasemen 25_26/klasemen bundesliga.xlsx
+++ b/klasemen 25_26/klasemen bundesliga.xlsx
@@ -1079,7 +1079,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
   <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1"/>
   </ignoredErrors>
